--- a/FornecedoresAtivos.xlsx
+++ b/FornecedoresAtivos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8612" uniqueCount="8612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8630" uniqueCount="8630">
   <si>
     <t>FORN_CNPJ</t>
   </si>
@@ -17966,7 +17966,7 @@
     <t>00000000009526</t>
   </si>
   <si>
-    <t>JBCLEAN COIFS LTDA</t>
+    <t>JB CLEAN COIFAS LTDA.</t>
   </si>
   <si>
     <t>JBCLEAN COIFAS</t>
@@ -24923,7 +24923,7 @@
     <t>00000000010199</t>
   </si>
   <si>
-    <t>MWB GESTÃO INTEG. E NEGOCIOS COM. LTDA.</t>
+    <t>MWB GESTÃO INTEG. E NEGÓCIOS COM. LTDA.</t>
   </si>
   <si>
     <t>MWB GESTÃO</t>
@@ -25583,7 +25583,7 @@
     <t>00000000010258</t>
   </si>
   <si>
-    <t xml:space="preserve">BELLOOBRAS SOL.  MATERIAIS DE CONSTRUÇÃO</t>
+    <t>BELLOOBRAS SOL. MATERIAIS DE CONST. LTDA</t>
   </si>
   <si>
     <t>BELLOOBRAS</t>
@@ -25811,6 +25811,21 @@
     <t>MARCENARIA FINA, MARCENARIA COOPERATIVA</t>
   </si>
   <si>
+    <t>00000000010284</t>
+  </si>
+  <si>
+    <t>FRENA SEGURAANÇA LTDA</t>
+  </si>
+  <si>
+    <t>FRENA SEGURANÇA</t>
+  </si>
+  <si>
+    <t>32475000</t>
+  </si>
+  <si>
+    <t>BLOCO DE CONCRETO ESTRUTURAL, MÃO DE OBRA TERCEIRIZADA, SERVIÇOS DE SEGURANÇA PATRIMONIAL</t>
+  </si>
+  <si>
     <t>00000000010282</t>
   </si>
   <si>
@@ -25836,6 +25851,45 @@
   </si>
   <si>
     <t>21030050</t>
+  </si>
+  <si>
+    <t>00000000010283</t>
+  </si>
+  <si>
+    <t>TANAKO CASA E CONSTRUÇÃO</t>
+  </si>
+  <si>
+    <t>TANAKO MATERIAIS</t>
+  </si>
+  <si>
+    <t>30468990</t>
+  </si>
+  <si>
+    <t>FERRAMENTAS, AÇO, DESMOLDANTES, ARTEFATOS DE CONCRETO, BRITA, ARGAMASSA PRÉ-FABRICADA, AREIA, ADITIVOS, CIMENTO, REJUNTES, CAL, GESSO, AGREGADOS E ENSACADOS DIVERSOS, GRAUTES, MATERIAL ELÉTRICO, MATERIAL HIDRÁULICO E ESGOTO, LUMINÁRIAS, ACABAMENTOS DE INTERRUPTOR E TOMADA, TIJOLO CERÂMICO, TELHA EM FIBROCIMENTO, CERÂMICA E PORCELANATO, PASTILHA, MADEIRA DE CONSTRUÇÃO, LOUÇAS, METAIS E ACESSÓRIOS, ARTEFATOS EM AÇO INOX, PREGOS, REBITES, CHUMBADORES QUÍMICOS, COLAS E ADESIVOS</t>
+  </si>
+  <si>
+    <t>00000000010285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLR AUDIO VIDEO  AUTOMAÇÃO E COMERCIO LT</t>
+  </si>
+  <si>
+    <t>JLR AUDIO</t>
+  </si>
+  <si>
+    <t>CAÇAMBAS E RETIRADAS DE ENTULHO, SERV. DE LÓGICA, TELEFONE, SOM E ANTENA</t>
+  </si>
+  <si>
+    <t>00000000010286</t>
+  </si>
+  <si>
+    <t>ELETRICA HAPAIA LTDA</t>
+  </si>
+  <si>
+    <t>ELETRICA HAPIA</t>
+  </si>
+  <si>
+    <t>967600051</t>
   </si>
   <si>
     <t>00000000010280</t>
@@ -26142,7 +26196,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K2003"/>
+  <dimension ref="A1:K2007"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1" style="1"/>
@@ -94174,27 +94228,29 @@
         <v>8601</v>
       </c>
       <c r="D2001" s="1" t="s">
-        <v>2580</v>
+        <v>1572</v>
       </c>
       <c r="E2001" s="1" t="s">
         <v>8602</v>
       </c>
       <c r="F2001" s="1" t="s">
-        <v>386</v>
+        <v>581</v>
       </c>
       <c r="G2001" s="2">
-        <v>4104808</v>
+        <v>4208203</v>
       </c>
       <c r="H2001" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="I2001" s="3">
+        <v>46001</v>
+      </c>
+      <c r="J2001" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2001" s="1" t="s">
         <v>8603</v>
       </c>
-      <c r="I2001" s="3">
-        <v>45996</v>
-      </c>
-      <c r="J2001" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2001" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="2002">
       <c r="A2002" s="1" t="s">
@@ -94207,62 +94263,200 @@
         <v>8606</v>
       </c>
       <c r="D2002" s="1" t="s">
-        <v>14</v>
+        <v>2580</v>
       </c>
       <c r="E2002" s="1" t="s">
         <v>8607</v>
       </c>
       <c r="F2002" s="1" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="G2002" s="2">
-        <v>3304557</v>
+        <v>4104808</v>
       </c>
       <c r="H2002" s="1" t="s">
-        <v>17</v>
+        <v>8608</v>
       </c>
       <c r="I2002" s="3">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="J2002" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K2002" s="1" t="s">
-        <v>323</v>
-      </c>
+      <c r="K2002" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="2003">
       <c r="A2003" s="1" t="s">
-        <v>8608</v>
+        <v>8609</v>
       </c>
       <c r="B2003" s="1" t="s">
-        <v>8609</v>
+        <v>8610</v>
       </c>
       <c r="C2003" s="1" t="s">
-        <v>8610</v>
+        <v>8611</v>
       </c>
       <c r="D2003" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2003" s="1" t="s">
+        <v>8612</v>
+      </c>
+      <c r="F2003" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2003" s="2">
+        <v>3304557</v>
+      </c>
+      <c r="H2003" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2003" s="3">
+        <v>45993</v>
+      </c>
+      <c r="J2003" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2003" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2004">
+      <c r="A2004" s="1" t="s">
+        <v>8613</v>
+      </c>
+      <c r="B2004" s="1" t="s">
+        <v>8614</v>
+      </c>
+      <c r="C2004" s="1" t="s">
+        <v>8615</v>
+      </c>
+      <c r="D2004" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E2004" s="1" t="s">
+        <v>8616</v>
+      </c>
+      <c r="F2004" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G2004" s="2">
+        <v>4208203</v>
+      </c>
+      <c r="H2004" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="I2004" s="3">
+        <v>46000</v>
+      </c>
+      <c r="J2004" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2004" s="1" t="s">
+        <v>8617</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2005">
+      <c r="A2005" s="1" t="s">
+        <v>8618</v>
+      </c>
+      <c r="B2005" s="1" t="s">
+        <v>8619</v>
+      </c>
+      <c r="C2005" s="1" t="s">
+        <v>8620</v>
+      </c>
+      <c r="D2005" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2005" s="1" t="s">
+        <v>8284</v>
+      </c>
+      <c r="F2005" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2005" s="2">
+        <v>3305109</v>
+      </c>
+      <c r="H2005" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="I2005" s="3">
+        <v>46001</v>
+      </c>
+      <c r="J2005" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2005" s="1" t="s">
+        <v>8621</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2006">
+      <c r="A2006" s="1" t="s">
+        <v>8622</v>
+      </c>
+      <c r="B2006" s="1" t="s">
+        <v>8623</v>
+      </c>
+      <c r="C2006" s="1" t="s">
+        <v>8624</v>
+      </c>
+      <c r="D2006" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E2003" s="1" t="s">
-        <v>8611</v>
-      </c>
-      <c r="F2003" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2003" s="2">
+      <c r="E2006" s="1" t="s">
+        <v>8625</v>
+      </c>
+      <c r="F2006" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2006" s="2">
+        <v>3550308</v>
+      </c>
+      <c r="H2006" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2006" s="3">
+        <v>46001</v>
+      </c>
+      <c r="J2006" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2006" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2007">
+      <c r="A2007" s="1" t="s">
+        <v>8626</v>
+      </c>
+      <c r="B2007" s="1" t="s">
+        <v>8627</v>
+      </c>
+      <c r="C2007" s="1" t="s">
+        <v>8628</v>
+      </c>
+      <c r="D2007" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2007" s="1" t="s">
+        <v>8629</v>
+      </c>
+      <c r="F2007" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2007" s="2">
         <v>3530607</v>
       </c>
-      <c r="H2003" s="1" t="s">
+      <c r="H2007" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="I2003" s="3">
+      <c r="I2007" s="3">
         <v>45995</v>
       </c>
-      <c r="J2003" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2003" s="1" t="s">
+      <c r="J2007" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2007" s="1" t="s">
         <v>547</v>
       </c>
     </row>

--- a/FornecedoresAtivos.xlsx
+++ b/FornecedoresAtivos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8630" uniqueCount="8630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8642" uniqueCount="8642">
   <si>
     <t>FORN_CNPJ</t>
   </si>
@@ -25890,6 +25890,42 @@
   </si>
   <si>
     <t>967600051</t>
+  </si>
+  <si>
+    <t>00000000010287</t>
+  </si>
+  <si>
+    <t>PRO IRON ESTRUTURA METALICA LTDA</t>
+  </si>
+  <si>
+    <t>PRO IRON</t>
+  </si>
+  <si>
+    <t>988352328</t>
+  </si>
+  <si>
+    <t>00000000010288</t>
+  </si>
+  <si>
+    <t>JR TRANSPORTES DE CARGAS LTDA</t>
+  </si>
+  <si>
+    <t>JR TRANSPORTE</t>
+  </si>
+  <si>
+    <t>999844351</t>
+  </si>
+  <si>
+    <t>00000000010289</t>
+  </si>
+  <si>
+    <t>TIPFORM LOCAÇÕES DE EQUIPAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>TIPFORM</t>
+  </si>
+  <si>
+    <t>24411178</t>
   </si>
   <si>
     <t>00000000010280</t>
@@ -26196,7 +26232,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K2007"/>
+  <dimension ref="A1:K2010"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1" style="1"/>
@@ -94436,27 +94472,132 @@
         <v>8628</v>
       </c>
       <c r="D2007" s="1" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="E2007" s="1" t="s">
         <v>8629</v>
       </c>
       <c r="F2007" s="1" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="G2007" s="2">
+        <v>3304904</v>
+      </c>
+      <c r="H2007" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I2007" s="3">
+        <v>46003</v>
+      </c>
+      <c r="J2007" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2007" s="1" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2008">
+      <c r="A2008" s="1" t="s">
+        <v>8630</v>
+      </c>
+      <c r="B2008" s="1" t="s">
+        <v>8631</v>
+      </c>
+      <c r="C2008" s="1" t="s">
+        <v>8632</v>
+      </c>
+      <c r="D2008" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E2008" s="1" t="s">
+        <v>8633</v>
+      </c>
+      <c r="F2008" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2008" s="2">
+        <v>4101804</v>
+      </c>
+      <c r="H2008" s="1" t="s">
+        <v>4081</v>
+      </c>
+      <c r="I2008" s="3">
+        <v>46003</v>
+      </c>
+      <c r="J2008" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2008" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2009">
+      <c r="A2009" s="1" t="s">
+        <v>8634</v>
+      </c>
+      <c r="B2009" s="1" t="s">
+        <v>8635</v>
+      </c>
+      <c r="C2009" s="1" t="s">
+        <v>8636</v>
+      </c>
+      <c r="D2009" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2009" s="1" t="s">
+        <v>8637</v>
+      </c>
+      <c r="F2009" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2009" s="2">
+        <v>3304557</v>
+      </c>
+      <c r="H2009" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2009" s="3">
+        <v>46003</v>
+      </c>
+      <c r="J2009" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2009" s="1" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2010">
+      <c r="A2010" s="1" t="s">
+        <v>8638</v>
+      </c>
+      <c r="B2010" s="1" t="s">
+        <v>8639</v>
+      </c>
+      <c r="C2010" s="1" t="s">
+        <v>8640</v>
+      </c>
+      <c r="D2010" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2010" s="1" t="s">
+        <v>8641</v>
+      </c>
+      <c r="F2010" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2010" s="2">
         <v>3530607</v>
       </c>
-      <c r="H2007" s="1" t="s">
+      <c r="H2010" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="I2007" s="3">
+      <c r="I2010" s="3">
         <v>45995</v>
       </c>
-      <c r="J2007" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2007" s="1" t="s">
+      <c r="J2010" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2010" s="1" t="s">
         <v>547</v>
       </c>
     </row>

--- a/FornecedoresAtivos.xlsx
+++ b/FornecedoresAtivos.xlsx
@@ -25568,7 +25568,7 @@
     <t>00000000010256</t>
   </si>
   <si>
-    <t>RZ9 LOCAÇÃO DE MAQUINAS E EQUIPAMENTOS L</t>
+    <t>RZ9 LOCAÇÃO DE MÁQUINAS E EQUIP. LTDA.</t>
   </si>
   <si>
     <t xml:space="preserve">RZ9  LOCAÇÃO</t>
@@ -25745,7 +25745,7 @@
     <t>00000000010272</t>
   </si>
   <si>
-    <t>STAN ELETRICA LTDA</t>
+    <t>STAN ELÉTRICA LTDA.</t>
   </si>
   <si>
     <t>979418630</t>

--- a/FornecedoresAtivos.xlsx
+++ b/FornecedoresAtivos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8799" uniqueCount="8799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8815" uniqueCount="8815">
   <si>
     <t>FORN_CNPJ</t>
   </si>
@@ -6470,7 +6470,7 @@
     <t>00000000007427</t>
   </si>
   <si>
-    <t xml:space="preserve">LMF 2012 COMERCIAL  MAT.CONSTRUÇÃO LTDA</t>
+    <t>LMF 2012 COMERCIAL MAT. CONSTRUÇÃO LTDA.</t>
   </si>
   <si>
     <t>SPW</t>
@@ -25574,7 +25574,7 @@
     <t>00000000010253</t>
   </si>
   <si>
-    <t>J L XAVIER LTDA</t>
+    <t>J.L. XAVIER LTDA.</t>
   </si>
   <si>
     <t>DEPOSITO BRASIL</t>
@@ -26409,6 +26409,54 @@
   </si>
   <si>
     <t>992921235</t>
+  </si>
+  <si>
+    <t>00000000010327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAN P LEITE  ME</t>
+  </si>
+  <si>
+    <t>YAN</t>
+  </si>
+  <si>
+    <t>982346622</t>
+  </si>
+  <si>
+    <t>00000000010328</t>
+  </si>
+  <si>
+    <t>BAYIT CONSTRUÇÕES LTDA</t>
+  </si>
+  <si>
+    <t>964500766</t>
+  </si>
+  <si>
+    <t>00000000010329</t>
+  </si>
+  <si>
+    <t>MTORRES CON. E RECUPERAÇÃO ESTRUTURAL</t>
+  </si>
+  <si>
+    <t>MTORRES CONSTRUÇÃO</t>
+  </si>
+  <si>
+    <t>25525861</t>
+  </si>
+  <si>
+    <t>ORÇAMENTOS E PLANEJAMENTOS, PROJETO ARQUITETURA E COMPLEMENTARES</t>
+  </si>
+  <si>
+    <t>00000000010330</t>
+  </si>
+  <si>
+    <t>ADERSON MATHIAS JUNZ FILHO LTDA</t>
+  </si>
+  <si>
+    <t>ADERSON MADEIRAS</t>
+  </si>
+  <si>
+    <t>33411012</t>
   </si>
 </sst>
 </file>
@@ -26703,7 +26751,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K2045"/>
+  <dimension ref="A1:K2049"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1" style="1"/>
@@ -96307,6 +96355,146 @@
         <v>2196</v>
       </c>
     </row>
+    <row ht="12.75" customHeight="1" r="2046">
+      <c r="A2046" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="B2046" s="1" t="s">
+        <v>8800</v>
+      </c>
+      <c r="C2046" s="1" t="s">
+        <v>8801</v>
+      </c>
+      <c r="D2046" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2046" s="1" t="s">
+        <v>8802</v>
+      </c>
+      <c r="F2046" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2046" s="2">
+        <v>3303500</v>
+      </c>
+      <c r="H2046" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I2046" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J2046" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2046" s="1" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2047">
+      <c r="A2047" s="1" t="s">
+        <v>8803</v>
+      </c>
+      <c r="B2047" s="1" t="s">
+        <v>8804</v>
+      </c>
+      <c r="C2047" s="1" t="s">
+        <v>3421</v>
+      </c>
+      <c r="D2047" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2047" s="1" t="s">
+        <v>8805</v>
+      </c>
+      <c r="F2047" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2047" s="2">
+        <v>3304557</v>
+      </c>
+      <c r="H2047" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2047" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J2047" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2047" s="1" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2048">
+      <c r="A2048" s="1" t="s">
+        <v>8806</v>
+      </c>
+      <c r="B2048" s="1" t="s">
+        <v>8807</v>
+      </c>
+      <c r="C2048" s="1" t="s">
+        <v>8808</v>
+      </c>
+      <c r="D2048" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2048" s="1" t="s">
+        <v>8809</v>
+      </c>
+      <c r="F2048" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2048" s="2">
+        <v>3304557</v>
+      </c>
+      <c r="H2048" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2048" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J2048" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2048" s="1" t="s">
+        <v>8810</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="2049">
+      <c r="A2049" s="1" t="s">
+        <v>8811</v>
+      </c>
+      <c r="B2049" s="1" t="s">
+        <v>8812</v>
+      </c>
+      <c r="C2049" s="1" t="s">
+        <v>8813</v>
+      </c>
+      <c r="D2049" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E2049" s="1" t="s">
+        <v>8814</v>
+      </c>
+      <c r="F2049" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G2049" s="2">
+        <v>4208203</v>
+      </c>
+      <c r="H2049" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="I2049" s="3">
+        <v>46063</v>
+      </c>
+      <c r="J2049" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2049" s="1" t="s">
+        <v>3882</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>
